--- a/Отчет_САО.xlsx
+++ b/Отчет_САО.xlsx
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>к-во</t>
+          <t>к-во/р.с</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
